--- a/data/personalia/6 YK.xlsx
+++ b/data/personalia/6 YK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBACFEEF-F688-46F4-89E5-18CEEC00B36C}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{A322B7DD-4C03-4789-9CEA-FB73339B58BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39C649FE-3137-4840-8596-5EE33ACD2DFB}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7016,6 +7016,9 @@
       <c r="K113" s="6">
         <v>45689</v>
       </c>
+      <c r="L113" s="6">
+        <v>46085</v>
+      </c>
       <c r="M113" s="6">
         <v>20455</v>
       </c>
@@ -7054,6 +7057,9 @@
       <c r="K114" s="6">
         <v>45689</v>
       </c>
+      <c r="L114" s="6">
+        <v>46085</v>
+      </c>
       <c r="M114" s="6">
         <v>20455</v>
       </c>
@@ -7698,6 +7704,9 @@
       </c>
       <c r="K129" s="6">
         <v>45689</v>
+      </c>
+      <c r="L129" s="6">
+        <v>46085</v>
       </c>
       <c r="M129" s="6">
         <v>20455</v>
